--- a/data/trans_bre/P1432-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P1432-Habitat-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 0,47</t>
+          <t>-1,72; 0,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,38</t>
+          <t>0,91; 3,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 2,12</t>
+          <t>-0,32; 2,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-86,35; 74,14</t>
+          <t>-88,8; 82,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>70,99; —</t>
+          <t>50,73; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,56; 506,97</t>
+          <t>-38,49; 512,28</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,8</t>
+          <t>-0,38; 1,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 1,86</t>
+          <t>-0,14; 1,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 1,48</t>
+          <t>-0,15; 1,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-34,3; 263,5</t>
+          <t>-33,02; 262,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-27,26; 660,51</t>
+          <t>-39,5; 659,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-27,81; 635,03</t>
+          <t>-31,98; 606,33</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,75</t>
+          <t>-0,59; 1,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 1,94</t>
+          <t>-0,38; 1,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,1; 2,36</t>
+          <t>0,27; 2,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-48,17; 377,66</t>
+          <t>-42,4; 365,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-40,69; 418,91</t>
+          <t>-41,24; 439,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,11; 1121,83</t>
+          <t>-6,6; 1345,36</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 1,89</t>
+          <t>-0,27; 1,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 1,52</t>
+          <t>-0,45; 1,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,27</t>
+          <t>0,42; 2,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-18,54; 298,17</t>
+          <t>-23,77; 274,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-41,2; 334,75</t>
+          <t>-38,32; 428,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,77; 1984,25</t>
+          <t>53,81; 2566,76</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 0,96</t>
+          <t>-0,19; 0,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,54</t>
+          <t>0,43; 1,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,45</t>
+          <t>0,49; 1,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,48; 112,56</t>
+          <t>-16,74; 103,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>49,2; 331,94</t>
+          <t>48,08; 338,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,3; 407,44</t>
+          <t>61,86; 371,26</t>
         </is>
       </c>
     </row>
